--- a/results/consolidated/Final_Dashboard.xlsx
+++ b/results/consolidated/Final_Dashboard.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Total Models Evaluated</t>
   </si>
   <si>
-    <t xml:space="preserve">25</t>
+    <t xml:space="preserve">19</t>
   </si>
   <si>
     <t xml:space="preserve">Chrono Split Results</t>
@@ -204,340 +204,343 @@
     <t xml:space="preserve">Chrono</t>
   </si>
   <si>
+    <t xml:space="preserve">std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KS_distance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasserstein_distance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tail_index_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skewness_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtosis_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tail_index_NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skewness_NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtosis_NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_KS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_KS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Wasserstein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_Wasserstein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Tail_index_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Skewness_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Kurtosis_Std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Tail_index_NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Skewness_NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Kurtosis_NF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset_Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volatility_clustering_persistence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volatility_clustering_first_sig_lag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volatility_clustering_acf_lag1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leverage_effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leverage_max_lag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Returns_ACF_lag1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squared_returns_ACF_lag1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autocorrelation_decay_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean_gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean_loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain_loss_asymmetry_ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skewness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_volatility_clustering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_leverage_effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_gain_loss_asymmetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_skewness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidence_Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VaR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_Exceedances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exceedance_Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected_Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupiec_pvalue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupiec_statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kupiec_reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christoffersen_pvalue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christoffersen_statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christoffersen_reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_exceedance_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_expected_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_kupiec_pvalue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_christoffersen_pvalue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kupiec_pass_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">christoffersen_pass_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_Observations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean_Return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volatility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max_Drawdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start_Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End_Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline_Volatility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volatility_Increase_Pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical_Crisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GFC_2008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008 Global Financial Crisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COVID_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COVID-19 Market Crash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypothetical_Shock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price_drop_30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30% price drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price_drop_50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50% price drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volatility_spike_2x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x volatility spike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volatility_spike_3x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3x volatility spike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_shift_down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative mean shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_volatility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_max_drawdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_volatility_increase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NF_GARCH_MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NF_GARCH_MAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard_GARCH_MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard_GARCH_MAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSE_Improvement_Pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_Test_Periods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_NF_GARCH_MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_Standard_GARCH_MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_MSE_Improvement_Pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_MAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median_AIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NF_GARCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">best_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_wins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">win_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pvalue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Significant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSE (NF &lt; Standard)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">less</t>
+  </si>
+  <si>
     <t xml:space="preserve">sstd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KS_distance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wasserstein_distance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tail_index_Std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skewness_Std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtosis_Std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tail_index_NF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skewness_NF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurtosis_NF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_KS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_KS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_Wasserstein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_Wasserstein</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_Tail_index_Std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_Skewness_Std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_Kurtosis_Std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_Tail_index_NF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_Skewness_NF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_Kurtosis_NF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset_Class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volatility_clustering_persistence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volatility_clustering_first_sig_lag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volatility_clustering_acf_lag1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leverage_effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leverage_max_lag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Returns_ACF_lag1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squared_returns_ACF_lag1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autocorrelation_decay_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean_gain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean_loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gain_loss_asymmetry_ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skewness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_volatility_clustering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_leverage_effect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_gain_loss_asymmetry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_skewness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidence_Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VaR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N_Exceedances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N_Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exceedance_Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected_Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupiec_pvalue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupiec_statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kupiec_reject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christoffersen_pvalue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christoffersen_statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christoffersen_reject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_exceedance_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_expected_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_kupiec_pvalue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_christoffersen_pvalue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kupiec_pass_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">christoffersen_pass_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N_Observations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean_Return</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volatility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max_Drawdown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start_Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End_Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline_Volatility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volatility_Increase_Pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical_Crisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GFC_2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2008 Global Financial Crisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COVID_2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COVID-19 Market Crash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypothetical_Shock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price_drop_30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30% price drop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">price_drop_50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50% price drop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volatility_spike_2x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2x volatility spike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volatility_spike_3x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3x volatility spike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_shift_down</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative mean shift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_volatility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_max_drawdown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_volatility_increase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NF_GARCH_MSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NF_GARCH_MAE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard_GARCH_MSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard_GARCH_MAE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSE_Improvement_Pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N_Test_Periods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_NF_GARCH_MSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_Standard_GARCH_MSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_MSE_Improvement_Pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_MSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_MAE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median_AIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NF_GARCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">best_source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_wins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">win_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test_Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pvalue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Significant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alternative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSE (NF &lt; Standard)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">less</t>
   </si>
   <si>
     <t xml:space="preserve">Best KS Distance Model</t>
@@ -912,10 +915,10 @@
         <v>-17476.4175403596</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000354121096211184</v>
+        <v>0.000354212298038953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0114829136709332</v>
+        <v>0.0114847621415467</v>
       </c>
       <c r="G2" t="n">
         <v>8762.1611360559</v>
@@ -935,10 +938,10 @@
         <v>-16456.3401877928</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000354965353094005</v>
+        <v>0.000354965793959046</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0114919689675483</v>
+        <v>0.0114915175328372</v>
       </c>
       <c r="G3" t="n">
         <v>8252.12245977249</v>
@@ -949,22 +952,22 @@
         <v>23</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>-16259.1952479916</v>
+        <v>-15337.514200342</v>
       </c>
       <c r="D4" t="n">
-        <v>-16232.2666991774</v>
+        <v>-15313.5777125072</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000362907234649055</v>
+        <v>0.00037150952613407</v>
       </c>
       <c r="F4" t="n">
-        <v>0.011656268602685</v>
+        <v>0.0118346604055098</v>
       </c>
       <c r="G4" t="n">
-        <v>8134.0976239958</v>
+        <v>7672.757100171</v>
       </c>
     </row>
     <row r="5">
@@ -981,10 +984,10 @@
         <v>671.691987241692</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000507650148030649</v>
+        <v>0.000505830603863818</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0161296690515369</v>
+        <v>0.0160926632878579</v>
       </c>
       <c r="G5" t="n">
         <v>-311.893627744737</v>
@@ -10128,7 +10131,7 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="C3" t="s">
         <v>167</v>
@@ -10151,7 +10154,7 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
         <v>167</v>
@@ -10174,7 +10177,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="C5" t="s">
         <v>167</v>
@@ -10228,19 +10231,19 @@
         <v>31</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000220734883384139</v>
+        <v>0.0000220806815155538</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000221056941595851</v>
+        <v>0.0000221097669885511</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00350197300933753</v>
+        <v>0.00350344167557607</v>
       </c>
     </row>
     <row r="3">
@@ -10248,19 +10251,19 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000342879023770953</v>
+        <v>0.0000342964198041262</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000343709846482227</v>
+        <v>0.0000343938185358085</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00431399553708906</v>
+        <v>0.0043159035708788</v>
       </c>
     </row>
     <row r="4">
@@ -10268,19 +10271,19 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000978526990960806</v>
+        <v>0.000098089951593645</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000982216702966197</v>
+        <v>0.0000983931333591145</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00764526738000115</v>
+        <v>0.00765821766830353</v>
       </c>
     </row>
     <row r="5">
@@ -10288,19 +10291,19 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000357254897325573</v>
+        <v>0.000357402335537457</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000363920522171209</v>
+        <v>0.000366056891137635</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0134469011394593</v>
+        <v>0.0134980501900651</v>
       </c>
     </row>
     <row r="6">
@@ -10308,19 +10311,19 @@
         <v>35</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004976064836022</v>
+        <v>0.000498049718244985</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000513811160649313</v>
+        <v>0.000517021391333054</v>
       </c>
       <c r="F6" t="n">
-        <v>0.016207168623693</v>
+        <v>0.0162815511778893</v>
       </c>
     </row>
     <row r="7">
@@ -10328,19 +10331,19 @@
         <v>36</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00111465389466928</v>
+        <v>0.00111480004288859</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00111838109282533</v>
+        <v>0.00111966997242023</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0242964491831583</v>
+        <v>0.0243017532470643</v>
       </c>
     </row>
   </sheetData>
@@ -10420,7 +10423,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -10428,15 +10431,15 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -10444,10 +10447,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -10501,10 +10504,10 @@
         <v>-13975.8085979135</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004976064836022</v>
+        <v>0.000498049718244985</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0158551210489624</v>
+        <v>0.0158566907824145</v>
       </c>
       <c r="G2" t="n">
         <v>7011.85666483284</v>
@@ -10527,10 +10530,10 @@
         <v>-13169.881565409</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000499331428163572</v>
+        <v>0.000499299334420236</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0158667967078021</v>
+        <v>0.0158651585390775</v>
       </c>
       <c r="G3" t="n">
         <v>6608.89314858061</v>
@@ -10544,22 +10547,22 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>-13905.261927556</v>
+        <v>635.787255489474</v>
       </c>
       <c r="D4" t="n">
-        <v>-13875.3413177625</v>
+        <v>671.691987241692</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000499561834646966</v>
+        <v>0.000505830603863818</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0158725642079564</v>
+        <v>0.0160926632878579</v>
       </c>
       <c r="G4" t="n">
-        <v>6957.63096377799</v>
+        <v>-311.893627744737</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -10570,22 +10573,22 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>635.787255489474</v>
+        <v>-11081.523323752</v>
       </c>
       <c r="D5" t="n">
-        <v>671.691987241692</v>
+        <v>-11057.5868359172</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000507650148030649</v>
+        <v>0.000564905908803178</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0161296690515369</v>
+        <v>0.0173116921022071</v>
       </c>
       <c r="G5" t="n">
-        <v>-311.893627744737</v>
+        <v>5544.76166187601</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -10593,28 +10596,28 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>-11081.523323752</v>
+        <v>-20390.7246340714</v>
       </c>
       <c r="D6" t="n">
-        <v>-11057.5868359172</v>
+        <v>-20354.8199023192</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000564905908803178</v>
+        <v>0.0000220806815155538</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0173116921022071</v>
+        <v>0.00350059548461617</v>
       </c>
       <c r="G6" t="n">
-        <v>5544.76166187601</v>
+        <v>10201.3623170357</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -10631,16 +10634,16 @@
         <v>-21183.5237417036</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0000220734883384139</v>
+        <v>0.0000220899886058771</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0034986759293063</v>
+        <v>0.00350315431501287</v>
       </c>
       <c r="G7" t="n">
         <v>10615.7142367279</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -10648,77 +10651,77 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>-20390.7246340714</v>
+        <v>-19372.7663740109</v>
       </c>
       <c r="D8" t="n">
-        <v>-20354.8199023192</v>
+        <v>-19348.829886176</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000220780623595792</v>
+        <v>0.0000221586308442225</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00350005998084207</v>
+        <v>0.00350657522709918</v>
       </c>
       <c r="G8" t="n">
-        <v>10201.3623170357</v>
+        <v>9690.38318700543</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>-21086.222814587</v>
+        <v>-21922.1562477529</v>
       </c>
       <c r="D9" t="n">
-        <v>-21056.3022047935</v>
+        <v>-21886.2515160007</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0000221125950961247</v>
+        <v>0.0000342964198041262</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00350258090010257</v>
+        <v>0.00431375960712445</v>
       </c>
       <c r="G9" t="n">
-        <v>10548.1114072935</v>
+        <v>10967.0781238764</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>-19372.7663740109</v>
+        <v>-20093.9832449172</v>
       </c>
       <c r="D10" t="n">
-        <v>-19348.829886176</v>
+        <v>-20070.0467570823</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000221586308442225</v>
+        <v>0.000034380430021123</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00350657522709918</v>
+        <v>0.00431437218736813</v>
       </c>
       <c r="G10" t="n">
-        <v>9690.38318700543</v>
+        <v>10050.9916224586</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -10726,126 +10729,126 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>-21922.1562477529</v>
+        <v>-20663.0629217926</v>
       </c>
       <c r="D11" t="n">
-        <v>-21886.2515160007</v>
+        <v>-20627.1581900404</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000342879023770953</v>
+        <v>0.0000345046057821764</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00430993310253984</v>
+        <v>0.00431957891814382</v>
       </c>
       <c r="G11" t="n">
-        <v>10967.0781238764</v>
+        <v>10337.5314608963</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>-21446.4359075332</v>
+        <v>-16714.5673553433</v>
       </c>
       <c r="D12" t="n">
-        <v>-21416.5152977397</v>
+        <v>-16678.6626235911</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0000343134264060025</v>
+        <v>0.000357402335537457</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00431232536809715</v>
+        <v>0.0133117347345129</v>
       </c>
       <c r="G12" t="n">
-        <v>10728.2179537666</v>
+        <v>8363.28367767167</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>-20093.9832449172</v>
+        <v>-15439.990288026</v>
       </c>
       <c r="D13" t="n">
-        <v>-20070.0467570823</v>
+        <v>-15404.0855562738</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000034380430021123</v>
+        <v>0.000360533639688918</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00431437218736813</v>
+        <v>0.0133476875206534</v>
       </c>
       <c r="G13" t="n">
-        <v>10050.9916224586</v>
+        <v>7725.99514401299</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>-20663.0629217926</v>
+        <v>-13915.8189354138</v>
       </c>
       <c r="D14" t="n">
-        <v>-20627.1581900404</v>
+        <v>-13891.882447579</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00003450217978867</v>
+        <v>0.000380234698186531</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00431935149035112</v>
+        <v>0.0138347283150291</v>
       </c>
       <c r="G14" t="n">
-        <v>10337.5314608963</v>
+        <v>6961.90946770692</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>-16187.7828771156</v>
+        <v>-11957.8877932379</v>
       </c>
       <c r="D15" t="n">
-        <v>-16157.8622673221</v>
+        <v>-11921.9830614857</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000357254897325573</v>
+        <v>0.00111480004288859</v>
       </c>
       <c r="F15" t="n">
-        <v>0.013288167989599</v>
+        <v>0.0242348350428466</v>
       </c>
       <c r="G15" t="n">
-        <v>8098.89143855781</v>
+        <v>5984.94389661896</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -10853,25 +10856,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>-16714.5673553433</v>
+        <v>-13272.5886735945</v>
       </c>
       <c r="D16" t="n">
-        <v>-16678.6626235911</v>
+        <v>-13236.6839418423</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000357676173393736</v>
+        <v>0.00111534537444763</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0133166881652794</v>
+        <v>0.0243047025513129</v>
       </c>
       <c r="G16" t="n">
-        <v>8363.28367767167</v>
+        <v>6642.29433679725</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -10879,25 +10882,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>-15439.990288026</v>
+        <v>-10849.6298936207</v>
       </c>
       <c r="D17" t="n">
-        <v>-15404.0855562738</v>
+        <v>-10825.6934057859</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000360516319778998</v>
+        <v>0.00112886449992447</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0133480200879298</v>
+        <v>0.0243657221470333</v>
       </c>
       <c r="G17" t="n">
-        <v>7725.99514401299</v>
+        <v>5428.81494681033</v>
       </c>
       <c r="H17" t="n">
         <v>3</v>
@@ -10905,236 +10908,80 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>-13915.8189354138</v>
+        <v>-17933.4795528587</v>
       </c>
       <c r="D18" t="n">
-        <v>-13891.882447579</v>
+        <v>-17897.5748211065</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000380234698186531</v>
+        <v>0.000098089951593645</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0138347283150291</v>
+        <v>0.00761853085890284</v>
       </c>
       <c r="G18" t="n">
-        <v>6961.90946770692</v>
+        <v>8972.73977642934</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>-12618.2868051962</v>
+        <v>-16711.3634303374</v>
       </c>
       <c r="D19" t="n">
-        <v>-12588.3661954027</v>
+        <v>-16687.4269425026</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00111465389466928</v>
+        <v>0.0000985129890248958</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0242801108181927</v>
+        <v>0.00767487245432214</v>
       </c>
       <c r="G19" t="n">
-        <v>6314.14340259809</v>
+        <v>8359.6817151687</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20" t="n">
-        <v>-11957.8877932379</v>
+        <v>-17296.0175829807</v>
       </c>
       <c r="D20" t="n">
-        <v>-11921.9830614857</v>
+        <v>-17260.1128512285</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001114776146248</v>
+        <v>0.0000985764594588027</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0242357836266807</v>
+        <v>0.00768124969168561</v>
       </c>
       <c r="G20" t="n">
-        <v>5984.94389661896</v>
+        <v>8654.00879149036</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-13272.5886735945</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-13236.6839418423</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.00111522983045958</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.0243041801407263</v>
-      </c>
-      <c r="G21" t="n">
-        <v>6642.29433679725</v>
-      </c>
-      <c r="H21" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-10849.6298936207</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-10825.6934057859</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.00112886449992447</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.0243657221470333</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5428.81494681033</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-17933.4795528587</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-17897.5748211065</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.0000978526990960806</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.00761288363878511</v>
-      </c>
-      <c r="G23" t="n">
-        <v>8972.73977642934</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-17841.2674418593</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-17811.3468320658</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.000097933010840291</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.00761151151521311</v>
-      </c>
-      <c r="G24" t="n">
-        <v>8925.63372092964</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-16711.3634303374</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-16687.4269425026</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.0000985129890248958</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.00767487245432214</v>
-      </c>
-      <c r="G25" t="n">
-        <v>8359.6817151687</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-17296.0175829807</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-17260.1128512285</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.0000985879822252114</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.00768180191168424</v>
-      </c>
-      <c r="G26" t="n">
-        <v>8654.00879149036</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -12006,7 +11853,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -12015,22 +11862,22 @@
         <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>-21086.222814587</v>
+        <v>-21219.4284734558</v>
       </c>
       <c r="E8" t="n">
-        <v>-21056.3022047935</v>
+        <v>-21183.5237417036</v>
       </c>
       <c r="F8" t="n">
-        <v>10548.1114072935</v>
+        <v>10615.7142367279</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000221125950961247</v>
+        <v>0.0000220899886058771</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00350258090010257</v>
+        <v>0.00350315431501287</v>
       </c>
       <c r="I8" t="n">
-        <v>6126.97657444797</v>
+        <v>6223.74448177264</v>
       </c>
       <c r="J8" t="n">
         <v>1000</v>
@@ -12041,7 +11888,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>57</v>
@@ -12050,22 +11897,22 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>-21446.4359075332</v>
+        <v>-21922.1562477529</v>
       </c>
       <c r="E9" t="n">
-        <v>-21416.5152977397</v>
+        <v>-21886.2515160007</v>
       </c>
       <c r="F9" t="n">
-        <v>10728.2179537666</v>
+        <v>10967.0781238764</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0000343134264060025</v>
+        <v>0.0000342964198041262</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00431232536809715</v>
+        <v>0.00431375960712445</v>
       </c>
       <c r="I9" t="n">
-        <v>5499.50128709555</v>
+        <v>5902.8244011558</v>
       </c>
       <c r="J9" t="n">
         <v>1000</v>
@@ -12076,7 +11923,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>57</v>
@@ -12085,22 +11932,22 @@
         <v>33</v>
       </c>
       <c r="D10" t="n">
-        <v>-17841.2674418593</v>
+        <v>-17933.4795528587</v>
       </c>
       <c r="E10" t="n">
-        <v>-17811.3468320658</v>
+        <v>-17897.5748211065</v>
       </c>
       <c r="F10" t="n">
-        <v>8925.63372092964</v>
+        <v>8972.73977642934</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000097933010840291</v>
+        <v>0.000098089951593645</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00761151151521311</v>
+        <v>0.00761853085890284</v>
       </c>
       <c r="I10" t="n">
-        <v>4578.68296307645</v>
+        <v>4861.56207368077</v>
       </c>
       <c r="J10" t="n">
         <v>1000</v>
@@ -12111,7 +11958,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>57</v>
@@ -12120,22 +11967,22 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>-12618.2868051962</v>
+        <v>-13272.5886735945</v>
       </c>
       <c r="E11" t="n">
-        <v>-12588.3661954027</v>
+        <v>-13236.6839418423</v>
       </c>
       <c r="F11" t="n">
-        <v>6314.14340259809</v>
+        <v>6642.29433679725</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00111465389466928</v>
+        <v>0.00111534537444763</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0242801108181927</v>
+        <v>0.0243047025513129</v>
       </c>
       <c r="I11" t="n">
-        <v>2405.97318948381</v>
+        <v>-2067.25897115705</v>
       </c>
       <c r="J11" t="n">
         <v>1000</v>
@@ -12146,7 +11993,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>57</v>
@@ -12155,22 +12002,22 @@
         <v>34</v>
       </c>
       <c r="D12" t="n">
-        <v>-16187.7828771156</v>
+        <v>-16714.5673553433</v>
       </c>
       <c r="E12" t="n">
-        <v>-16157.8622673221</v>
+        <v>-16678.6626235911</v>
       </c>
       <c r="F12" t="n">
-        <v>8098.89143855781</v>
+        <v>8363.28367767167</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000357254897325573</v>
+        <v>0.000357402335537457</v>
       </c>
       <c r="H12" t="n">
-        <v>0.013288167989599</v>
+        <v>0.0133117347345129</v>
       </c>
       <c r="I12" t="n">
-        <v>3574.65152851914</v>
+        <v>3037.58715489622</v>
       </c>
       <c r="J12" t="n">
         <v>1000</v>
@@ -12181,7 +12028,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>57</v>
@@ -12190,22 +12037,22 @@
         <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>-13905.261927556</v>
+        <v>-14011.7133296657</v>
       </c>
       <c r="E13" t="n">
-        <v>-13875.3413177625</v>
+        <v>-13975.8085979135</v>
       </c>
       <c r="F13" t="n">
-        <v>6957.63096377799</v>
+        <v>7011.85666483284</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000499561834646966</v>
+        <v>0.000498049718244985</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0158725642079564</v>
+        <v>0.0158566907824145</v>
       </c>
       <c r="I13" t="n">
-        <v>3534.88880870559</v>
+        <v>3728.01895383072</v>
       </c>
       <c r="J13" t="n">
         <v>1000</v>
@@ -12216,31 +12063,31 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
         <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>-21219.4284734558</v>
+        <v>635.787255489474</v>
       </c>
       <c r="E14" t="n">
-        <v>-21183.5237417036</v>
+        <v>671.691987241692</v>
       </c>
       <c r="F14" t="n">
-        <v>10615.7142367279</v>
+        <v>-311.893627744737</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0000220734883384139</v>
+        <v>0.000505830603863818</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0034986759293063</v>
+        <v>0.0160926632878579</v>
       </c>
       <c r="I14" t="n">
-        <v>6236.36806595074</v>
+        <v>3529.32316862138</v>
       </c>
       <c r="J14" t="n">
         <v>1000</v>
@@ -12251,31 +12098,31 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
         <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>-21922.1562477529</v>
+        <v>-20390.7246340714</v>
       </c>
       <c r="E15" t="n">
-        <v>-21886.2515160007</v>
+        <v>-20354.8199023192</v>
       </c>
       <c r="F15" t="n">
-        <v>10967.0781238764</v>
+        <v>10201.3623170357</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0000342879023770953</v>
+        <v>0.0000220806815155538</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00430993310253984</v>
+        <v>0.00350059548461617</v>
       </c>
       <c r="I15" t="n">
-        <v>5898.69094610072</v>
+        <v>-1211.44723357436</v>
       </c>
       <c r="J15" t="n">
         <v>1000</v>
@@ -12286,31 +12133,31 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>-17933.4795528587</v>
+        <v>-20663.0629217926</v>
       </c>
       <c r="E16" t="n">
-        <v>-17897.5748211065</v>
+        <v>-20627.1581900404</v>
       </c>
       <c r="F16" t="n">
-        <v>8972.73977642934</v>
+        <v>10337.5314608963</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000978526990960806</v>
+        <v>0.0000345046057821764</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00761288363878511</v>
+        <v>0.00431957891814382</v>
       </c>
       <c r="I16" t="n">
-        <v>4844.06105502113</v>
+        <v>-803.811410289445</v>
       </c>
       <c r="J16" t="n">
         <v>1000</v>
@@ -12321,31 +12168,31 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>-13272.5886735945</v>
+        <v>-17296.0175829807</v>
       </c>
       <c r="E17" t="n">
-        <v>-13236.6839418423</v>
+        <v>-17260.1128512285</v>
       </c>
       <c r="F17" t="n">
-        <v>6642.29433679725</v>
+        <v>8654.00879149036</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00111522983045958</v>
+        <v>0.0000985764594588027</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0243041801407263</v>
+        <v>0.00768124969168561</v>
       </c>
       <c r="I17" t="n">
-        <v>-2036.78567964723</v>
+        <v>-2819.25534825357</v>
       </c>
       <c r="J17" t="n">
         <v>1000</v>
@@ -12356,31 +12203,31 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>-16714.5673553433</v>
+        <v>-11957.8877932379</v>
       </c>
       <c r="E18" t="n">
-        <v>-16678.6626235911</v>
+        <v>-11921.9830614857</v>
       </c>
       <c r="F18" t="n">
-        <v>8363.28367767167</v>
+        <v>5984.94389661896</v>
       </c>
       <c r="G18" t="n">
-        <v>0.000357676173393736</v>
+        <v>0.00111480004288859</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0133166881652794</v>
+        <v>0.0242348350428466</v>
       </c>
       <c r="I18" t="n">
-        <v>3041.55719520702</v>
+        <v>-6011.46874657578</v>
       </c>
       <c r="J18" t="n">
         <v>1000</v>
@@ -12391,31 +12238,31 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
         <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>-14011.7133296657</v>
+        <v>-15439.990288026</v>
       </c>
       <c r="E19" t="n">
-        <v>-13975.8085979135</v>
+        <v>-15404.0855562738</v>
       </c>
       <c r="F19" t="n">
-        <v>7011.85666483284</v>
+        <v>7725.99514401299</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004976064836022</v>
+        <v>0.000360533639688918</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0158551210489624</v>
+        <v>0.0133476875206534</v>
       </c>
       <c r="I19" t="n">
-        <v>3721.83023101062</v>
+        <v>-3639.58444911581</v>
       </c>
       <c r="J19" t="n">
         <v>1000</v>
@@ -12426,7 +12273,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
         <v>57</v>
@@ -12435,237 +12282,27 @@
         <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>635.787255489474</v>
+        <v>-13205.7862971612</v>
       </c>
       <c r="E20" t="n">
-        <v>671.691987241692</v>
+        <v>-13169.881565409</v>
       </c>
       <c r="F20" t="n">
-        <v>-311.893627744737</v>
+        <v>6608.89314858061</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000507650148030649</v>
+        <v>0.000499299334420236</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0161296690515369</v>
+        <v>0.0158651585390775</v>
       </c>
       <c r="I20" t="n">
-        <v>3535.2605011815</v>
+        <v>-5132.65281526239</v>
       </c>
       <c r="J20" t="n">
         <v>1000</v>
       </c>
       <c r="K20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-20390.7246340714</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-20354.8199023192</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10201.3623170357</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0000220780623595792</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.00350005998084207</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-841.128167265488</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-20663.0629217926</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-20627.1581900404</v>
-      </c>
-      <c r="F22" t="n">
-        <v>10337.5314608963</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.00003450217978867</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00431935149035112</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-740.941689798181</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-17296.0175829807</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-17260.1128512285</v>
-      </c>
-      <c r="F23" t="n">
-        <v>8654.00879149036</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.0000985879822252114</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00768180191168424</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-2675.00782728108</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-11957.8877932379</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-11921.9830614857</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5984.94389661896</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.001114776146248</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.0242357836266807</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-5945.51191729431</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-15439.990288026</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-15404.0855562738</v>
-      </c>
-      <c r="F25" t="n">
-        <v>7725.99514401299</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.000360516319778998</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.0133480200879298</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-4160.60447744878</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-13205.7862971612</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-13169.881565409</v>
-      </c>
-      <c r="F26" t="n">
-        <v>6608.89314858061</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.000499331428163572</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.0158667967078021</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-4888.94348585455</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K26" t="s">
         <v>56</v>
       </c>
     </row>

--- a/results/consolidated/Final_Dashboard.xlsx
+++ b/results/consolidated/Final_Dashboard.xlsx
@@ -915,10 +915,10 @@
         <v>-17476.4175403596</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000354212298038953</v>
+        <v>0.000354935416139937</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0114847621415467</v>
+        <v>0.0115132139121491</v>
       </c>
       <c r="G2" t="n">
         <v>8762.1611360559</v>
@@ -938,10 +938,10 @@
         <v>-16456.3401877928</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000354965793959046</v>
+        <v>0.000354980713573553</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0114915175328372</v>
+        <v>0.0114923112984004</v>
       </c>
       <c r="G3" t="n">
         <v>8252.12245977249</v>
@@ -961,10 +961,10 @@
         <v>-15313.5777125072</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00037150952613407</v>
+        <v>0.000372448659306713</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0118346604055098</v>
+        <v>0.0118570964909068</v>
       </c>
       <c r="G4" t="n">
         <v>7672.757100171</v>
@@ -984,10 +984,10 @@
         <v>671.691987241692</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000505830603863818</v>
+        <v>0.000553297503494059</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0160926632878579</v>
+        <v>0.0172362186738709</v>
       </c>
       <c r="G5" t="n">
         <v>-311.893627744737</v>
@@ -10237,13 +10237,13 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000220806815155538</v>
+        <v>0.0000220786970132616</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000221097669885511</v>
+        <v>0.0000221968489941737</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00350344167557607</v>
+        <v>0.00351102410240828</v>
       </c>
     </row>
     <row r="3">
@@ -10257,13 +10257,13 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000342964198041262</v>
+        <v>0.0000344300611238395</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000343938185358085</v>
+        <v>0.000034483084285608</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0043159035708788</v>
+        <v>0.00432724377058346</v>
       </c>
     </row>
     <row r="4">
@@ -10277,13 +10277,13 @@
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000098089951593645</v>
+        <v>0.000097968623664851</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0000983931333591145</v>
+        <v>0.0000986357154541356</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00765821766830353</v>
+        <v>0.00767325499820236</v>
       </c>
     </row>
     <row r="5">
@@ -10297,13 +10297,13 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000357402335537457</v>
+        <v>0.000356706471914379</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000366056891137635</v>
+        <v>0.000365721777467639</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0134980501900651</v>
+        <v>0.0134940567855586</v>
       </c>
     </row>
     <row r="6">
@@ -10314,16 +10314,16 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000498049718244985</v>
+        <v>0.000499492774893839</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000517021391333054</v>
+        <v>0.000530650258537762</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0162815511778893</v>
+        <v>0.0166099098928893</v>
       </c>
     </row>
     <row r="7">
@@ -10337,13 +10337,13 @@
         <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00111480004288859</v>
+        <v>0.0011147216977999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00111966997242023</v>
+        <v>0.00112059097495319</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0243017532470643</v>
+        <v>0.0243185234469312</v>
       </c>
     </row>
   </sheetData>
@@ -10495,22 +10495,22 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>-14011.7133296657</v>
+        <v>-13205.7862971612</v>
       </c>
       <c r="D2" t="n">
-        <v>-13975.8085979135</v>
+        <v>-13169.881565409</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000498049718244985</v>
+        <v>0.000499492774893839</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0158566907824145</v>
+        <v>0.0158690506333466</v>
       </c>
       <c r="G2" t="n">
-        <v>7011.85666483284</v>
+        <v>6608.89314858061</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -10521,22 +10521,22 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>-13205.7862971612</v>
+        <v>-14011.7133296657</v>
       </c>
       <c r="D3" t="n">
-        <v>-13169.881565409</v>
+        <v>-13975.8085979135</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000499299334420236</v>
+        <v>0.000502462606266766</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0158651585390775</v>
+        <v>0.0159696312552844</v>
       </c>
       <c r="G3" t="n">
-        <v>6608.89314858061</v>
+        <v>7011.85666483284</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -10556,10 +10556,10 @@
         <v>671.691987241692</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000505830603863818</v>
+        <v>0.000553297503494059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0160926632878579</v>
+        <v>0.0172362186738709</v>
       </c>
       <c r="G4" t="n">
         <v>-311.893627744737</v>
@@ -10582,10 +10582,10 @@
         <v>-11057.5868359172</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000564905908803178</v>
+        <v>0.000567348149496385</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0173116921022071</v>
+        <v>0.0173647390090551</v>
       </c>
       <c r="G5" t="n">
         <v>5544.76166187601</v>
@@ -10608,10 +10608,10 @@
         <v>-20354.8199023192</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0000220806815155538</v>
+        <v>0.0000220786970132616</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00350059548461617</v>
+        <v>0.0035002379434319</v>
       </c>
       <c r="G6" t="n">
         <v>10201.3623170357</v>
@@ -10625,22 +10625,22 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>-21219.4284734558</v>
+        <v>-19372.7663740109</v>
       </c>
       <c r="D7" t="n">
-        <v>-21183.5237417036</v>
+        <v>-19348.829886176</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0000220899886058771</v>
+        <v>0.0000221502614205928</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00350315431501287</v>
+        <v>0.00350098170754738</v>
       </c>
       <c r="G7" t="n">
-        <v>10615.7142367279</v>
+        <v>9690.38318700543</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -10651,22 +10651,22 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>-19372.7663740109</v>
+        <v>-21219.4284734558</v>
       </c>
       <c r="D8" t="n">
-        <v>-19348.829886176</v>
+        <v>-21183.5237417036</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000221586308442225</v>
+        <v>0.0000223615885486666</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00350657522709918</v>
+        <v>0.00353185265624556</v>
       </c>
       <c r="G8" t="n">
-        <v>9690.38318700543</v>
+        <v>10615.7142367279</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -10686,10 +10686,10 @@
         <v>-21886.2515160007</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0000342964198041262</v>
+        <v>0.0000344300611238395</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00431375960712445</v>
+        <v>0.0043345000740643</v>
       </c>
       <c r="G9" t="n">
         <v>10967.0781238764</v>
@@ -10703,22 +10703,22 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>-20093.9832449172</v>
+        <v>-20663.0629217926</v>
       </c>
       <c r="D10" t="n">
-        <v>-20070.0467570823</v>
+        <v>-20627.1581900404</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000034380430021123</v>
+        <v>0.0000345013235870406</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00431437218736813</v>
+        <v>0.00431928121262559</v>
       </c>
       <c r="G10" t="n">
-        <v>10050.9916224586</v>
+        <v>10337.5314608963</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -10729,22 +10729,22 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>-20663.0629217926</v>
+        <v>-20093.9832449172</v>
       </c>
       <c r="D11" t="n">
-        <v>-20627.1581900404</v>
+        <v>-20070.0467570823</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0000345046057821764</v>
+        <v>0.0000345178681459439</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00431957891814382</v>
+        <v>0.00432795002506048</v>
       </c>
       <c r="G11" t="n">
-        <v>10337.5314608963</v>
+        <v>10050.9916224586</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -10764,10 +10764,10 @@
         <v>-16678.6626235911</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000357402335537457</v>
+        <v>0.000356706471914379</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0133117347345129</v>
+        <v>0.0132974872468535</v>
       </c>
       <c r="G12" t="n">
         <v>8363.28367767167</v>
@@ -10790,10 +10790,10 @@
         <v>-15404.0855562738</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000360533639688918</v>
+        <v>0.000360542263970232</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0133476875206534</v>
+        <v>0.0133511357442286</v>
       </c>
       <c r="G13" t="n">
         <v>7725.99514401299</v>
@@ -10816,10 +10816,10 @@
         <v>-13891.882447579</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000380234698186531</v>
+        <v>0.000379916596518305</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0138347283150291</v>
+        <v>0.0138335473655937</v>
       </c>
       <c r="G14" t="n">
         <v>6961.90946770692</v>
@@ -10842,10 +10842,10 @@
         <v>-11921.9830614857</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00111480004288859</v>
+        <v>0.0011147216977999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0242348350428466</v>
+        <v>0.0242338278694657</v>
       </c>
       <c r="G15" t="n">
         <v>5984.94389661896</v>
@@ -10868,10 +10868,10 @@
         <v>-13236.6839418423</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00111534537444763</v>
+        <v>0.00111568314532112</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0243047025513129</v>
+        <v>0.0243210237958923</v>
       </c>
       <c r="G16" t="n">
         <v>6642.29433679725</v>
@@ -10894,10 +10894,10 @@
         <v>-10825.6934057859</v>
       </c>
       <c r="E17" t="n">
-        <v>0.00112886449992447</v>
+        <v>0.00113136808173854</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0243657221470333</v>
+        <v>0.0244007186754356</v>
       </c>
       <c r="G17" t="n">
         <v>5428.81494681033</v>
@@ -10920,10 +10920,10 @@
         <v>-17897.5748211065</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000098089951593645</v>
+        <v>0.000097968623664851</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00761853085890284</v>
+        <v>0.00762478844455467</v>
       </c>
       <c r="G18" t="n">
         <v>8972.73977642934</v>
@@ -10937,22 +10937,22 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>-16711.3634303374</v>
+        <v>-17296.0175829807</v>
       </c>
       <c r="D19" t="n">
-        <v>-16687.4269425026</v>
+        <v>-17260.1128512285</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0000985129890248958</v>
+        <v>0.0000985475241770422</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00767487245432214</v>
+        <v>0.00768033438730387</v>
       </c>
       <c r="G19" t="n">
-        <v>8359.6817151687</v>
+        <v>8654.00879149036</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
@@ -10963,22 +10963,22 @@
         <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>-17296.0175829807</v>
+        <v>-16711.3634303374</v>
       </c>
       <c r="D20" t="n">
-        <v>-17260.1128512285</v>
+        <v>-16687.4269425026</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0000985764594588027</v>
+        <v>0.0000993909985205136</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00768124969168561</v>
+        <v>0.00771464216274853</v>
       </c>
       <c r="G20" t="n">
-        <v>8654.00879149036</v>
+        <v>8359.6817151687</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
@@ -11661,16 +11661,16 @@
         <v>9690.38318700543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0000221586308442225</v>
+        <v>0.0000221502614205928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00350657522709918</v>
+        <v>0.00350098170754738</v>
       </c>
       <c r="I2" t="n">
-        <v>6091.12355668695</v>
+        <v>5964.7368220389</v>
       </c>
       <c r="J2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K2" t="s">
         <v>56</v>
@@ -11696,16 +11696,16 @@
         <v>10050.9916224586</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000034380430021123</v>
+        <v>0.0000345178681459439</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00431437218736813</v>
+        <v>0.00432795002506048</v>
       </c>
       <c r="I3" t="n">
-        <v>5568.48559558248</v>
+        <v>5347.30986735</v>
       </c>
       <c r="J3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K3" t="s">
         <v>56</v>
@@ -11731,16 +11731,16 @@
         <v>8359.6817151687</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0000985129890248958</v>
+        <v>0.0000993909985205136</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00767487245432214</v>
+        <v>0.00771464216274853</v>
       </c>
       <c r="I4" t="n">
-        <v>4597.28223830732</v>
+        <v>4479.01481686913</v>
       </c>
       <c r="J4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K4" t="s">
         <v>56</v>
@@ -11766,16 +11766,16 @@
         <v>5428.81494681033</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00112886449992447</v>
+        <v>0.00113136808173854</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0243657221470333</v>
+        <v>0.0244007186754356</v>
       </c>
       <c r="I5" t="n">
-        <v>2332.45241615951</v>
+        <v>2207.29395744856</v>
       </c>
       <c r="J5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K5" t="s">
         <v>56</v>
@@ -11801,16 +11801,16 @@
         <v>6961.90946770692</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000380234698186531</v>
+        <v>0.000379916596518305</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0138347283150291</v>
+        <v>0.0138335473655937</v>
       </c>
       <c r="I6" t="n">
-        <v>3328.66132101524</v>
+        <v>3198.3897728614</v>
       </c>
       <c r="J6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K6" t="s">
         <v>56</v>
@@ -11836,16 +11836,16 @@
         <v>5544.76166187601</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000564905908803178</v>
+        <v>0.000567348149496385</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0173116921022071</v>
+        <v>0.0173647390090551</v>
       </c>
       <c r="I7" t="n">
-        <v>3298.7086956953</v>
+        <v>3153.80400473469</v>
       </c>
       <c r="J7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K7" t="s">
         <v>56</v>
@@ -11871,16 +11871,16 @@
         <v>10615.7142367279</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0000220899886058771</v>
+        <v>0.0000223615885486666</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00350315431501287</v>
+        <v>0.00353185265624556</v>
       </c>
       <c r="I8" t="n">
-        <v>6223.74448177264</v>
+        <v>6134.05590876226</v>
       </c>
       <c r="J8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K8" t="s">
         <v>56</v>
@@ -11906,16 +11906,16 @@
         <v>10967.0781238764</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0000342964198041262</v>
+        <v>0.0000344300611238395</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00431375960712445</v>
+        <v>0.0043345000740643</v>
       </c>
       <c r="I9" t="n">
-        <v>5902.8244011558</v>
+        <v>5835.55752941045</v>
       </c>
       <c r="J9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K9" t="s">
         <v>56</v>
@@ -11941,16 +11941,16 @@
         <v>8972.73977642934</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000098089951593645</v>
+        <v>0.000097968623664851</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00761853085890284</v>
+        <v>0.00762478844455467</v>
       </c>
       <c r="I10" t="n">
-        <v>4861.56207368077</v>
+        <v>4771.47952131575</v>
       </c>
       <c r="J10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K10" t="s">
         <v>56</v>
@@ -11976,16 +11976,16 @@
         <v>6642.29433679725</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00111534537444763</v>
+        <v>0.00111568314532112</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0243047025513129</v>
+        <v>0.0243210237958923</v>
       </c>
       <c r="I11" t="n">
-        <v>-2067.25897115705</v>
+        <v>-695.0019926656</v>
       </c>
       <c r="J11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K11" t="s">
         <v>56</v>
@@ -12011,16 +12011,16 @@
         <v>8363.28367767167</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000357402335537457</v>
+        <v>0.000356706471914379</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0133117347345129</v>
+        <v>0.0132974872468535</v>
       </c>
       <c r="I12" t="n">
-        <v>3037.58715489622</v>
+        <v>3197.58996884358</v>
       </c>
       <c r="J12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K12" t="s">
         <v>56</v>
@@ -12046,16 +12046,16 @@
         <v>7011.85666483284</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000498049718244985</v>
+        <v>0.000502462606266766</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0158566907824145</v>
+        <v>0.0159696312552844</v>
       </c>
       <c r="I13" t="n">
-        <v>3728.01895383072</v>
+        <v>3639.22496904861</v>
       </c>
       <c r="J13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K13" t="s">
         <v>56</v>
@@ -12081,16 +12081,16 @@
         <v>-311.893627744737</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000505830603863818</v>
+        <v>0.000553297503494059</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0160926632878579</v>
+        <v>0.0172362186738709</v>
       </c>
       <c r="I14" t="n">
-        <v>3529.32316862138</v>
+        <v>3496.4065642525</v>
       </c>
       <c r="J14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K14" t="s">
         <v>56</v>
@@ -12116,16 +12116,16 @@
         <v>10201.3623170357</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0000220806815155538</v>
+        <v>0.0000220786970132616</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00350059548461617</v>
+        <v>0.0035002379434319</v>
       </c>
       <c r="I15" t="n">
-        <v>-1211.44723357436</v>
+        <v>2253.61726177711</v>
       </c>
       <c r="J15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K15" t="s">
         <v>56</v>
@@ -12151,16 +12151,16 @@
         <v>10337.5314608963</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0000345046057821764</v>
+        <v>0.0000345013235870406</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00431957891814382</v>
+        <v>0.00431928121262559</v>
       </c>
       <c r="I16" t="n">
-        <v>-803.811410289445</v>
+        <v>2341.25927651771</v>
       </c>
       <c r="J16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K16" t="s">
         <v>56</v>
@@ -12186,16 +12186,16 @@
         <v>8654.00879149036</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0000985764594588027</v>
+        <v>0.0000985475241770422</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00768124969168561</v>
+        <v>0.00768033438730387</v>
       </c>
       <c r="I17" t="n">
-        <v>-2819.25534825357</v>
+        <v>621.379306545768</v>
       </c>
       <c r="J17" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K17" t="s">
         <v>56</v>
@@ -12221,16 +12221,16 @@
         <v>5984.94389661896</v>
       </c>
       <c r="G18" t="n">
-        <v>0.00111480004288859</v>
+        <v>0.0011147216977999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0242348350428466</v>
+        <v>0.0242338278694657</v>
       </c>
       <c r="I18" t="n">
-        <v>-6011.46874657578</v>
+        <v>-2224.45731256715</v>
       </c>
       <c r="J18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K18" t="s">
         <v>56</v>
@@ -12256,16 +12256,16 @@
         <v>7725.99514401299</v>
       </c>
       <c r="G19" t="n">
-        <v>0.000360533639688918</v>
+        <v>0.000360542263970232</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0133476875206534</v>
+        <v>0.0133511357442286</v>
       </c>
       <c r="I19" t="n">
-        <v>-3639.58444911581</v>
+        <v>-502.603671654493</v>
       </c>
       <c r="J19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K19" t="s">
         <v>56</v>
@@ -12291,16 +12291,16 @@
         <v>6608.89314858061</v>
       </c>
       <c r="G20" t="n">
-        <v>0.000499299334420236</v>
+        <v>0.000499492774893839</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0158651585390775</v>
+        <v>0.0158690506333466</v>
       </c>
       <c r="I20" t="n">
-        <v>-5132.65281526239</v>
+        <v>-1206.52535084575</v>
       </c>
       <c r="J20" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="K20" t="s">
         <v>56</v>

--- a/results/consolidated/Final_Dashboard.xlsx
+++ b/results/consolidated/Final_Dashboard.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -190,6 +190,24 @@
   </si>
   <si>
     <t xml:space="preserve">TGARCH_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBPCNY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBPZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURZAR</t>
   </si>
   <si>
     <t xml:space="preserve">Distribution</t>
@@ -1012,24 +1030,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B2" t="n">
         <v>1.81708516810632</v>
@@ -1046,7 +1064,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B3" t="n">
         <v>2.17414894164547</v>
@@ -1080,43 +1098,43 @@
         <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="K1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="M1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="O1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2">
@@ -3367,25 +3385,25 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="H1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2">
@@ -3612,37 +3630,37 @@
         <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="G1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="J1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="L1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2">
@@ -3650,13 +3668,13 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E2" t="n">
         <v>143</v>
@@ -3684,13 +3702,13 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E3" t="n">
         <v>59</v>
@@ -3718,13 +3736,13 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E4" t="n">
         <v>4515</v>
@@ -3752,13 +3770,13 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E5" t="n">
         <v>4515</v>
@@ -3786,13 +3804,13 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E6" t="n">
         <v>4515</v>
@@ -3820,13 +3838,13 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E7" t="n">
         <v>4515</v>
@@ -3854,13 +3872,13 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E8" t="n">
         <v>4515</v>
@@ -3888,13 +3906,13 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E9" t="n">
         <v>143</v>
@@ -3922,13 +3940,13 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E10" t="n">
         <v>59</v>
@@ -3956,13 +3974,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E11" t="n">
         <v>4515</v>
@@ -3990,13 +4008,13 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E12" t="n">
         <v>4515</v>
@@ -4024,13 +4042,13 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E13" t="n">
         <v>4515</v>
@@ -4058,13 +4076,13 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E14" t="n">
         <v>4515</v>
@@ -4092,13 +4110,13 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C15" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E15" t="n">
         <v>4515</v>
@@ -4126,13 +4144,13 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E16" t="n">
         <v>143</v>
@@ -4160,13 +4178,13 @@
         <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E17" t="n">
         <v>59</v>
@@ -4194,13 +4212,13 @@
         <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E18" t="n">
         <v>4515</v>
@@ -4228,13 +4246,13 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E19" t="n">
         <v>4515</v>
@@ -4262,13 +4280,13 @@
         <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E20" t="n">
         <v>4515</v>
@@ -4296,13 +4314,13 @@
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E21" t="n">
         <v>4515</v>
@@ -4330,13 +4348,13 @@
         <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E22" t="n">
         <v>4515</v>
@@ -4364,13 +4382,13 @@
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E23" t="n">
         <v>143</v>
@@ -4398,13 +4416,13 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E24" t="n">
         <v>59</v>
@@ -4432,13 +4450,13 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E25" t="n">
         <v>4515</v>
@@ -4466,13 +4484,13 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E26" t="n">
         <v>4515</v>
@@ -4500,13 +4518,13 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D27" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E27" t="n">
         <v>4515</v>
@@ -4534,13 +4552,13 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E28" t="n">
         <v>4515</v>
@@ -4568,13 +4586,13 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E29" t="n">
         <v>4515</v>
@@ -4602,13 +4620,13 @@
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E30" t="n">
         <v>143</v>
@@ -4636,13 +4654,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E31" t="n">
         <v>59</v>
@@ -4670,13 +4688,13 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E32" t="n">
         <v>4515</v>
@@ -4704,13 +4722,13 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E33" t="n">
         <v>4515</v>
@@ -4738,13 +4756,13 @@
         <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E34" t="n">
         <v>4515</v>
@@ -4772,13 +4790,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E35" t="n">
         <v>4515</v>
@@ -4806,13 +4824,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D36" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E36" t="n">
         <v>4515</v>
@@ -4840,13 +4858,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E37" t="n">
         <v>143</v>
@@ -4874,13 +4892,13 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E38" t="n">
         <v>59</v>
@@ -4908,13 +4926,13 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E39" t="n">
         <v>4515</v>
@@ -4942,13 +4960,13 @@
         <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E40" t="n">
         <v>4515</v>
@@ -4976,13 +4994,13 @@
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D41" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E41" t="n">
         <v>4515</v>
@@ -5010,13 +5028,13 @@
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D42" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E42" t="n">
         <v>4515</v>
@@ -5044,13 +5062,13 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D43" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E43" t="n">
         <v>4515</v>
@@ -5086,30 +5104,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C1" t="s">
         <v>16</v>
       </c>
       <c r="D1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
@@ -5124,10 +5142,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
@@ -5142,10 +5160,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
@@ -5162,10 +5180,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
@@ -5182,10 +5200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B6" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
@@ -5202,10 +5220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -5222,10 +5240,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
@@ -5256,31 +5274,31 @@
         <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D1" t="s">
         <v>15</v>
       </c>
       <c r="E1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="H1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2">
@@ -5288,10 +5306,10 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -5314,10 +5332,10 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -5346,10 +5364,10 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -5378,10 +5396,10 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -5404,10 +5422,10 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -5430,10 +5448,10 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -5462,10 +5480,10 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -5494,10 +5512,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -5520,10 +5538,10 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -5552,10 +5570,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -5584,10 +5602,10 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
@@ -5610,10 +5628,10 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -5642,10 +5660,10 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -5674,10 +5692,10 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C15" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
@@ -5700,10 +5718,10 @@
         <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
@@ -5732,10 +5750,10 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -5764,10 +5782,10 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
@@ -5790,10 +5808,10 @@
         <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
@@ -5822,10 +5840,10 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -5854,10 +5872,10 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
@@ -5880,10 +5898,10 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D22" t="s">
         <v>22</v>
@@ -5912,10 +5930,10 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -5944,10 +5962,10 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
         <v>23</v>
@@ -5970,10 +5988,10 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
@@ -6002,10 +6020,10 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -6034,10 +6052,10 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D27" t="s">
         <v>23</v>
@@ -6060,10 +6078,10 @@
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D28" t="s">
         <v>24</v>
@@ -6086,10 +6104,10 @@
         <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
         <v>22</v>
@@ -6118,10 +6136,10 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -6150,10 +6168,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D31" t="s">
         <v>23</v>
@@ -6176,10 +6194,10 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
         <v>22</v>
@@ -6208,10 +6226,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -6240,10 +6258,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
         <v>23</v>
@@ -6266,10 +6284,10 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
         <v>22</v>
@@ -6298,10 +6316,10 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -6330,10 +6348,10 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D37" t="s">
         <v>23</v>
@@ -6356,10 +6374,10 @@
         <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D38" t="s">
         <v>22</v>
@@ -6388,10 +6406,10 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -6420,10 +6438,10 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
         <v>23</v>
@@ -6446,10 +6464,10 @@
         <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D41" t="s">
         <v>22</v>
@@ -6478,10 +6496,10 @@
         <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -6510,10 +6528,10 @@
         <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D43" t="s">
         <v>23</v>
@@ -6536,10 +6554,10 @@
         <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
@@ -6562,10 +6580,10 @@
         <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D45" t="s">
         <v>22</v>
@@ -6594,10 +6612,10 @@
         <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -6626,10 +6644,10 @@
         <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D47" t="s">
         <v>23</v>
@@ -6652,10 +6670,10 @@
         <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D48" t="s">
         <v>22</v>
@@ -6684,10 +6702,10 @@
         <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -6716,10 +6734,10 @@
         <v>33</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D50" t="s">
         <v>23</v>
@@ -6742,10 +6760,10 @@
         <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D51" t="s">
         <v>22</v>
@@ -6774,10 +6792,10 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -6806,10 +6824,10 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C53" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
         <v>23</v>
@@ -6832,10 +6850,10 @@
         <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C54" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D54" t="s">
         <v>22</v>
@@ -6864,10 +6882,10 @@
         <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C55" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -6896,10 +6914,10 @@
         <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C56" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D56" t="s">
         <v>23</v>
@@ -6922,10 +6940,10 @@
         <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C57" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D57" t="s">
         <v>22</v>
@@ -6954,10 +6972,10 @@
         <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C58" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -6986,10 +7004,10 @@
         <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C59" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D59" t="s">
         <v>23</v>
@@ -7012,10 +7030,10 @@
         <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D60" t="s">
         <v>22</v>
@@ -7044,10 +7062,10 @@
         <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C61" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -7076,10 +7094,10 @@
         <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C62" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D62" t="s">
         <v>23</v>
@@ -7102,10 +7120,10 @@
         <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C63" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D63" t="s">
         <v>22</v>
@@ -7134,10 +7152,10 @@
         <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C64" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
@@ -7166,10 +7184,10 @@
         <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C65" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D65" t="s">
         <v>23</v>
@@ -7192,10 +7210,10 @@
         <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D66" t="s">
         <v>22</v>
@@ -7224,10 +7242,10 @@
         <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C67" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -7256,10 +7274,10 @@
         <v>36</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C68" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D68" t="s">
         <v>23</v>
@@ -7282,10 +7300,10 @@
         <v>36</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C69" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D69" t="s">
         <v>22</v>
@@ -7314,10 +7332,10 @@
         <v>36</v>
       </c>
       <c r="B70" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C70" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
@@ -7346,10 +7364,10 @@
         <v>36</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C71" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D71" t="s">
         <v>23</v>
@@ -7372,10 +7390,10 @@
         <v>36</v>
       </c>
       <c r="B72" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C72" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D72" t="s">
         <v>24</v>
@@ -7398,10 +7416,10 @@
         <v>36</v>
       </c>
       <c r="B73" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C73" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D73" t="s">
         <v>22</v>
@@ -7430,10 +7448,10 @@
         <v>36</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C74" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
@@ -7462,10 +7480,10 @@
         <v>36</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C75" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D75" t="s">
         <v>23</v>
@@ -7488,10 +7506,10 @@
         <v>36</v>
       </c>
       <c r="B76" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C76" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D76" t="s">
         <v>24</v>
@@ -7514,10 +7532,10 @@
         <v>36</v>
       </c>
       <c r="B77" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C77" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D77" t="s">
         <v>22</v>
@@ -7546,10 +7564,10 @@
         <v>36</v>
       </c>
       <c r="B78" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C78" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -7578,10 +7596,10 @@
         <v>36</v>
       </c>
       <c r="B79" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C79" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D79" t="s">
         <v>23</v>
@@ -7604,10 +7622,10 @@
         <v>36</v>
       </c>
       <c r="B80" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C80" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
@@ -7630,10 +7648,10 @@
         <v>36</v>
       </c>
       <c r="B81" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C81" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D81" t="s">
         <v>22</v>
@@ -7662,10 +7680,10 @@
         <v>36</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C82" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
@@ -7694,10 +7712,10 @@
         <v>36</v>
       </c>
       <c r="B83" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C83" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
@@ -7720,10 +7738,10 @@
         <v>36</v>
       </c>
       <c r="B84" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C84" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D84" t="s">
         <v>24</v>
@@ -7746,10 +7764,10 @@
         <v>36</v>
       </c>
       <c r="B85" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C85" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D85" t="s">
         <v>22</v>
@@ -7778,10 +7796,10 @@
         <v>36</v>
       </c>
       <c r="B86" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C86" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
@@ -7810,10 +7828,10 @@
         <v>36</v>
       </c>
       <c r="B87" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C87" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
         <v>23</v>
@@ -7836,10 +7854,10 @@
         <v>36</v>
       </c>
       <c r="B88" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C88" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D88" t="s">
         <v>24</v>
@@ -7862,10 +7880,10 @@
         <v>36</v>
       </c>
       <c r="B89" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C89" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D89" t="s">
         <v>22</v>
@@ -7894,10 +7912,10 @@
         <v>36</v>
       </c>
       <c r="B90" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C90" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D90" t="s">
         <v>11</v>
@@ -7926,10 +7944,10 @@
         <v>36</v>
       </c>
       <c r="B91" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C91" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D91" t="s">
         <v>23</v>
@@ -7952,10 +7970,10 @@
         <v>36</v>
       </c>
       <c r="B92" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C92" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D92" t="s">
         <v>22</v>
@@ -7984,10 +8002,10 @@
         <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C93" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
@@ -8016,10 +8034,10 @@
         <v>34</v>
       </c>
       <c r="B94" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C94" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D94" t="s">
         <v>23</v>
@@ -8042,10 +8060,10 @@
         <v>34</v>
       </c>
       <c r="B95" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C95" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D95" t="s">
         <v>22</v>
@@ -8074,10 +8092,10 @@
         <v>34</v>
       </c>
       <c r="B96" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C96" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
@@ -8106,10 +8124,10 @@
         <v>34</v>
       </c>
       <c r="B97" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C97" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D97" t="s">
         <v>23</v>
@@ -8132,10 +8150,10 @@
         <v>34</v>
       </c>
       <c r="B98" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C98" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D98" t="s">
         <v>22</v>
@@ -8164,10 +8182,10 @@
         <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C99" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
@@ -8196,10 +8214,10 @@
         <v>34</v>
       </c>
       <c r="B100" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C100" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D100" t="s">
         <v>23</v>
@@ -8222,10 +8240,10 @@
         <v>34</v>
       </c>
       <c r="B101" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C101" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D101" t="s">
         <v>22</v>
@@ -8254,10 +8272,10 @@
         <v>34</v>
       </c>
       <c r="B102" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C102" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D102" t="s">
         <v>11</v>
@@ -8286,10 +8304,10 @@
         <v>34</v>
       </c>
       <c r="B103" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C103" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D103" t="s">
         <v>23</v>
@@ -8312,10 +8330,10 @@
         <v>34</v>
       </c>
       <c r="B104" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C104" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D104" t="s">
         <v>22</v>
@@ -8344,10 +8362,10 @@
         <v>34</v>
       </c>
       <c r="B105" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C105" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
@@ -8376,10 +8394,10 @@
         <v>34</v>
       </c>
       <c r="B106" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D106" t="s">
         <v>23</v>
@@ -8402,10 +8420,10 @@
         <v>34</v>
       </c>
       <c r="B107" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C107" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D107" t="s">
         <v>22</v>
@@ -8434,10 +8452,10 @@
         <v>34</v>
       </c>
       <c r="B108" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C108" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D108" t="s">
         <v>11</v>
@@ -8466,10 +8484,10 @@
         <v>34</v>
       </c>
       <c r="B109" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C109" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D109" t="s">
         <v>23</v>
@@ -8492,10 +8510,10 @@
         <v>34</v>
       </c>
       <c r="B110" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C110" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D110" t="s">
         <v>22</v>
@@ -8524,10 +8542,10 @@
         <v>34</v>
       </c>
       <c r="B111" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C111" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D111" t="s">
         <v>11</v>
@@ -8556,10 +8574,10 @@
         <v>34</v>
       </c>
       <c r="B112" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C112" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D112" t="s">
         <v>23</v>
@@ -8582,10 +8600,10 @@
         <v>34</v>
       </c>
       <c r="B113" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C113" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D113" t="s">
         <v>24</v>
@@ -8608,10 +8626,10 @@
         <v>34</v>
       </c>
       <c r="B114" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C114" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D114" t="s">
         <v>22</v>
@@ -8640,10 +8658,10 @@
         <v>34</v>
       </c>
       <c r="B115" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D115" t="s">
         <v>11</v>
@@ -8672,10 +8690,10 @@
         <v>35</v>
       </c>
       <c r="B116" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C116" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D116" t="s">
         <v>23</v>
@@ -8698,10 +8716,10 @@
         <v>35</v>
       </c>
       <c r="B117" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C117" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D117" t="s">
         <v>22</v>
@@ -8730,10 +8748,10 @@
         <v>35</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C118" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D118" t="s">
         <v>11</v>
@@ -8762,10 +8780,10 @@
         <v>35</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C119" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D119" t="s">
         <v>23</v>
@@ -8788,10 +8806,10 @@
         <v>35</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C120" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D120" t="s">
         <v>24</v>
@@ -8820,10 +8838,10 @@
         <v>35</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C121" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D121" t="s">
         <v>22</v>
@@ -8852,10 +8870,10 @@
         <v>35</v>
       </c>
       <c r="B122" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C122" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D122" t="s">
         <v>11</v>
@@ -8884,10 +8902,10 @@
         <v>35</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C123" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D123" t="s">
         <v>23</v>
@@ -8910,10 +8928,10 @@
         <v>35</v>
       </c>
       <c r="B124" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C124" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D124" t="s">
         <v>22</v>
@@ -8942,10 +8960,10 @@
         <v>35</v>
       </c>
       <c r="B125" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C125" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D125" t="s">
         <v>11</v>
@@ -8974,10 +8992,10 @@
         <v>35</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C126" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D126" t="s">
         <v>23</v>
@@ -9000,10 +9018,10 @@
         <v>35</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C127" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D127" t="s">
         <v>22</v>
@@ -9032,10 +9050,10 @@
         <v>35</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C128" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D128" t="s">
         <v>11</v>
@@ -9064,10 +9082,10 @@
         <v>35</v>
       </c>
       <c r="B129" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C129" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
         <v>23</v>
@@ -9090,10 +9108,10 @@
         <v>35</v>
       </c>
       <c r="B130" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C130" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D130" t="s">
         <v>22</v>
@@ -9122,10 +9140,10 @@
         <v>35</v>
       </c>
       <c r="B131" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C131" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D131" t="s">
         <v>11</v>
@@ -9154,10 +9172,10 @@
         <v>35</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C132" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D132" t="s">
         <v>23</v>
@@ -9180,10 +9198,10 @@
         <v>35</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C133" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D133" t="s">
         <v>22</v>
@@ -9212,10 +9230,10 @@
         <v>35</v>
       </c>
       <c r="B134" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D134" t="s">
         <v>11</v>
@@ -9244,10 +9262,10 @@
         <v>35</v>
       </c>
       <c r="B135" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C135" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D135" t="s">
         <v>23</v>
@@ -9270,10 +9288,10 @@
         <v>35</v>
       </c>
       <c r="B136" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C136" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D136" t="s">
         <v>22</v>
@@ -9302,10 +9320,10 @@
         <v>35</v>
       </c>
       <c r="B137" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C137" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D137" t="s">
         <v>11</v>
@@ -9342,7 +9360,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B1" t="s">
         <v>15</v>
@@ -9351,18 +9369,18 @@
         <v>16</v>
       </c>
       <c r="D1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -9382,7 +9400,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
@@ -9402,7 +9420,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -9422,7 +9440,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -9438,7 +9456,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -9458,7 +9476,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -9478,7 +9496,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -9494,7 +9512,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -9514,7 +9532,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -9530,7 +9548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -9550,7 +9568,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
@@ -9566,7 +9584,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -9586,7 +9604,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
@@ -9602,7 +9620,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -9622,7 +9640,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
@@ -9638,7 +9656,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -9658,7 +9676,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
@@ -9674,7 +9692,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s">
         <v>11</v>
@@ -9694,7 +9712,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -9710,7 +9728,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
@@ -9730,7 +9748,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s">
         <v>24</v>
@@ -9746,7 +9764,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -9766,7 +9784,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -9782,7 +9800,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
@@ -9802,7 +9820,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B26" t="s">
         <v>24</v>
@@ -9818,7 +9836,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
@@ -9838,7 +9856,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B28" t="s">
         <v>23</v>
@@ -9865,10 +9883,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C1" t="s">
         <v>16</v>
@@ -9877,27 +9895,27 @@
         <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F1" t="s">
         <v>20</v>
       </c>
       <c r="G1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H1" t="s">
         <v>17</v>
       </c>
       <c r="I1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -9923,10 +9941,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -9952,10 +9970,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -9981,10 +9999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -10021,24 +10039,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
@@ -10049,10 +10067,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -10063,10 +10081,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -10091,22 +10109,22 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
@@ -10114,10 +10132,10 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D2" t="n">
         <v>15</v>
@@ -10129,7 +10147,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3">
@@ -10137,10 +10155,10 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -10152,7 +10170,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4">
@@ -10160,10 +10178,10 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -10175,7 +10193,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
@@ -10183,10 +10201,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -10198,7 +10216,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -10429,7 +10447,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
@@ -10437,15 +10455,15 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -10453,10 +10471,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -11029,13 +11047,13 @@
         <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>6665.84245598496</v>
+        <v>6691.43647276878</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -11049,13 +11067,13 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>6515.04308953379</v>
+        <v>6552.21046936049</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -11069,13 +11087,13 @@
         <v>51</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>6693.4201197412</v>
+        <v>6688.60992188574</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -11089,13 +11107,13 @@
         <v>52</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>6707.43511247273</v>
+        <v>6729.98006266365</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -11109,13 +11127,13 @@
         <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>8249.41915490284</v>
+        <v>8269.00800505899</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -11129,13 +11147,13 @@
         <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>8138.60432906824</v>
+        <v>8173.71250800092</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -11149,13 +11167,13 @@
         <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>8269.85132847719</v>
+        <v>8284.11155025666</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -11169,13 +11187,13 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>8287.55158312122</v>
+        <v>8301.24129117383</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -11183,19 +11201,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
         <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>7381.62399687174</v>
+        <v>9503.83979486227</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -11203,19 +11221,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>7288.96939554192</v>
+        <v>9410.47417011801</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -11223,19 +11241,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>51</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>7328.57150909967</v>
+        <v>9516.73275003668</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -11243,19 +11261,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
         <v>52</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>7435.10350556254</v>
+        <v>9528.42783811264</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -11263,19 +11281,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>11072.5747623311</v>
+        <v>7738.96879769429</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -11283,19 +11301,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
         <v>50</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>11003.0280469814</v>
+        <v>7605.31602911709</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -11303,19 +11321,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
         <v>51</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>10783.9129915726</v>
+        <v>7706.94390352311</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -11323,19 +11341,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
         <v>52</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>11112.218545703</v>
+        <v>7792.0567013605</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -11343,19 +11361,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>11033.515576734</v>
+        <v>9178.72681344229</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -11363,39 +11381,39 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
         <v>50</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>11014.3807167135</v>
+        <v>9135.27726688144</v>
       </c>
       <c r="F19" t="n">
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
         <v>51</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>10868.7687603931</v>
+        <v>9148.17348224461</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -11403,19 +11421,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
         <v>52</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>11072.2545410679</v>
+        <v>9204.36612264923</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -11423,19 +11441,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
         <v>49</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>9211.58448935649</v>
+        <v>7436.42699472546</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -11443,19 +11461,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
         <v>50</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>-420.567501327054</v>
+        <v>7352.72075903996</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -11463,19 +11481,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>9190.3468447269</v>
+        <v>7403.52475425271</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -11483,21 +11501,501 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
         <v>52</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>9286.88073754697</v>
+        <v>7487.41213086616</v>
       </c>
       <c r="F25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>11131.823420292</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11068.6973745361</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10842.2363175825</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11187.5690915366</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11072.5850531077</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7757.18711569745</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10901.1842811189</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11113.3601932458</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>11054.8447092587</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10971.423130234</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10906.7135133944</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11118.3428962144</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9244.74738944564</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9247.48440432385</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9216.91291812306</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9327.44398491009</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>9518.23900418248</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>9530.62943050709</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9371.63063166915</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>9571.29707415968</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9588.71329615966</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" t="n">
+        <v>9620.59328494843</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9626.0461625731</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" t="n">
+        <v>9654.81375685666</v>
+      </c>
+      <c r="F49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11517,7 +12015,7 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
         <v>25</v>
@@ -11538,13 +12036,13 @@
         <v>40</v>
       </c>
       <c r="I1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
@@ -11552,7 +12050,7 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
@@ -11579,7 +12077,7 @@
         <v>100</v>
       </c>
       <c r="K2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -11587,7 +12085,7 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
@@ -11614,7 +12112,7 @@
         <v>100</v>
       </c>
       <c r="K3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
@@ -11622,7 +12120,7 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -11649,7 +12147,7 @@
         <v>100</v>
       </c>
       <c r="K4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -11657,7 +12155,7 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
         <v>36</v>
@@ -11684,7 +12182,7 @@
         <v>100</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -11692,7 +12190,7 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -11719,7 +12217,7 @@
         <v>100</v>
       </c>
       <c r="K6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -11727,7 +12225,7 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
         <v>35</v>
@@ -11754,7 +12252,7 @@
         <v>100</v>
       </c>
       <c r="K7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -11762,7 +12260,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
@@ -11789,7 +12287,7 @@
         <v>100</v>
       </c>
       <c r="K8" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -11797,7 +12295,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -11824,7 +12322,7 @@
         <v>100</v>
       </c>
       <c r="K9" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -11832,7 +12330,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
         <v>33</v>
@@ -11859,7 +12357,7 @@
         <v>100</v>
       </c>
       <c r="K10" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -11867,7 +12365,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
@@ -11894,7 +12392,7 @@
         <v>100</v>
       </c>
       <c r="K11" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -11902,7 +12400,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
@@ -11929,7 +12427,7 @@
         <v>100</v>
       </c>
       <c r="K12" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -11937,7 +12435,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
         <v>35</v>
@@ -11964,7 +12462,7 @@
         <v>100</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -11972,7 +12470,7 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
         <v>35</v>
@@ -11999,7 +12497,7 @@
         <v>100</v>
       </c>
       <c r="K14" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -12007,7 +12505,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -12034,7 +12532,7 @@
         <v>100</v>
       </c>
       <c r="K15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -12042,7 +12540,7 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
@@ -12069,7 +12567,7 @@
         <v>100</v>
       </c>
       <c r="K16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -12077,7 +12575,7 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -12104,7 +12602,7 @@
         <v>100</v>
       </c>
       <c r="K17" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
@@ -12112,7 +12610,7 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
         <v>36</v>
@@ -12139,7 +12637,7 @@
         <v>100</v>
       </c>
       <c r="K18" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
@@ -12147,7 +12645,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
@@ -12174,7 +12672,7 @@
         <v>100</v>
       </c>
       <c r="K19" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -12182,7 +12680,7 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
         <v>35</v>
@@ -12209,7 +12707,7 @@
         <v>100</v>
       </c>
       <c r="K20" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -12251,13 +12749,13 @@
         <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>6665.84245598496</v>
+        <v>6691.43647276878</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -12271,13 +12769,13 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>6515.04308953379</v>
+        <v>6552.21046936049</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -12291,13 +12789,13 @@
         <v>51</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>6693.4201197412</v>
+        <v>6688.60992188574</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -12311,13 +12809,13 @@
         <v>52</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>6707.43511247273</v>
+        <v>6729.98006266365</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -12331,13 +12829,13 @@
         <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>8249.41915490284</v>
+        <v>8269.00800505899</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -12351,13 +12849,13 @@
         <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>8138.60432906824</v>
+        <v>8173.71250800092</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -12371,13 +12869,13 @@
         <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>8269.85132847719</v>
+        <v>8284.11155025666</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -12391,13 +12889,13 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>8287.55158312122</v>
+        <v>8301.24129117383</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -12405,19 +12903,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
         <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>7381.62399687174</v>
+        <v>9503.83979486227</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -12425,19 +12923,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>7288.96939554192</v>
+        <v>9410.47417011801</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -12445,19 +12943,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>51</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>7328.57150909967</v>
+        <v>9516.73275003668</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -12465,19 +12963,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
         <v>52</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>7435.10350556254</v>
+        <v>9528.42783811264</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -12485,19 +12983,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>11072.5747623311</v>
+        <v>7738.96879769429</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -12505,19 +13003,19 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
         <v>50</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>11003.0280469814</v>
+        <v>7605.31602911709</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -12525,19 +13023,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
         <v>51</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>10783.9129915726</v>
+        <v>7706.94390352311</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -12545,19 +13043,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
         <v>52</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>11112.218545703</v>
+        <v>7792.0567013605</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -12565,19 +13063,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>11033.515576734</v>
+        <v>9178.72681344229</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -12585,39 +13083,39 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
         <v>50</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>11014.3807167135</v>
+        <v>9135.27726688144</v>
       </c>
       <c r="F19" t="n">
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
         <v>51</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>10868.7687603931</v>
+        <v>9148.17348224461</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -12625,19 +13123,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
         <v>52</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>11072.2545410679</v>
+        <v>9204.36612264923</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -12645,19 +13143,19 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
         <v>49</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>9211.58448935649</v>
+        <v>7436.42699472546</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -12665,19 +13163,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
         <v>50</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>-420.567501327054</v>
+        <v>7352.72075903996</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -12685,19 +13183,19 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>9190.3468447269</v>
+        <v>7403.52475425271</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -12705,21 +13203,501 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
         <v>52</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>9286.88073754697</v>
+        <v>7487.41213086616</v>
       </c>
       <c r="F25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>11131.823420292</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11068.6973745361</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10842.2363175825</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11187.5690915366</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11072.5850531077</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7757.18711569745</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>10901.1842811189</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11113.3601932458</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>11054.8447092587</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10971.423130234</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10906.7135133944</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11118.3428962144</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9244.74738944564</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9247.48440432385</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9216.91291812306</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9327.44398491009</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>9518.23900418248</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>9530.62943050709</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9371.63063166915</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>9571.29707415968</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9588.71329615966</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" t="n">
+        <v>9620.59328494843</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9626.0461625731</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" t="n">
+        <v>9654.81375685666</v>
+      </c>
+      <c r="F49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12742,28 +13720,28 @@
         <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
@@ -13374,34 +14352,34 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2">
@@ -13540,43 +14518,43 @@
         <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="N1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
@@ -13584,7 +14562,7 @@
         <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n">
         <v>1.54939388672019</v>
@@ -13628,7 +14606,7 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C3" t="n">
         <v>2.47896518229883</v>
@@ -13672,7 +14650,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C4" t="n">
         <v>1.42289643529993</v>
@@ -13716,7 +14694,7 @@
         <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
         <v>2.17245464849179</v>
@@ -13760,7 +14738,7 @@
         <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C6" t="n">
         <v>1.87447132794184</v>
@@ -13804,7 +14782,7 @@
         <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
         <v>2.47552084850278</v>
